--- a/mobileteacherold.xlsx
+++ b/mobileteacherold.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mega\Projects\Python\byrnecellphone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4187BB86-467D-4959-B30F-822FA7594C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B3AD95-B101-434F-9CFF-6BCD43DCAB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="55">
   <si>
-    <t>How often do you notice the students in class comply with the new cell phone policy?</t>
-  </si>
-  <si>
-    <t>How easy has the new cell phone policy been to enforce in your classes?</t>
-  </si>
-  <si>
     <t>13 years or more</t>
   </si>
   <si>
@@ -190,6 +184,12 @@
   </si>
   <si>
     <t>dominicT</t>
+  </si>
+  <si>
+    <t>often</t>
+  </si>
+  <si>
+    <t>easy</t>
   </si>
 </sst>
 </file>
@@ -287,8 +287,8 @@
   <tableColumns count="12">
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="years" dataDxfId="11"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="signif" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="How often do you notice the students in class comply with the new cell phone policy?" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="How easy has the new cell phone policy been to enforce in your classes?" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="often" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="easy" dataDxfId="8"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="diff" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="influ" dataDxfId="6"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="prod" dataDxfId="5"/>
@@ -607,110 +607,110 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>52</v>
-      </c>
-      <c r="K1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -718,16 +718,16 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -739,13 +739,13 @@
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -753,16 +753,16 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -774,33 +774,33 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>2</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -812,33 +812,33 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -864,16 +864,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -885,13 +885,13 @@
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -899,16 +899,16 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -934,16 +934,16 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
         <v>2</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>4</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -990,13 +990,13 @@
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1004,55 +1004,55 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
         <v>3</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>5</v>
-      </c>
       <c r="I12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
         <v>2</v>
       </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
-      </c>
       <c r="E13">
         <v>7</v>
       </c>
@@ -1063,13 +1063,13 @@
         <v>7</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1077,16 +1077,16 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1098,33 +1098,33 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1136,33 +1136,33 @@
         <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1174,33 +1174,33 @@
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -1212,33 +1212,33 @@
         <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>10</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -1250,33 +1250,33 @@
         <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B19">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -1288,13 +1288,13 @@
         <v>10</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -1302,54 +1302,54 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" t="s">
         <v>21</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
-      <c r="H20" t="s">
-        <v>23</v>
-      </c>
       <c r="I20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>6</v>
@@ -1361,13 +1361,13 @@
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>7</v>
@@ -1375,17 +1375,17 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
         <v>2</v>
       </c>
-      <c r="B22">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s">
-        <v>4</v>
-      </c>
       <c r="E22">
         <v>7</v>
       </c>
@@ -1396,13 +1396,13 @@
         <v>7</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -1410,16 +1410,16 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1431,33 +1431,33 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24">
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -1469,13 +1469,13 @@
         <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -1483,16 +1483,16 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -1504,33 +1504,33 @@
         <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -1542,13 +1542,13 @@
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -1556,16 +1556,16 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B27">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>6</v>
@@ -1577,13 +1577,13 @@
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -1591,16 +1591,16 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1612,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K28">
         <v>8</v>
@@ -1626,16 +1626,16 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B29">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -1647,19 +1647,19 @@
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
